--- a/Process_Cost_Library.xlsx
+++ b/Process_Cost_Library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0693660-AB5D-46A4-82A6-FF43E7C5CA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78AB2379-9CC6-441A-A021-CA3D5701EDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{97C44FE3-4B91-4BC8-AACA-B84D84603B31}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Technology</t>
   </si>
@@ -78,30 +78,14 @@
   </si>
   <si>
     <t>1.1</t>
-  </si>
-  <si>
-    <t>Investment Casting</t>
-  </si>
-  <si>
-    <t>1.18</t>
-  </si>
-  <si>
-    <t>Sand Casting</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -128,13 +112,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -471,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62863C3B-FFEF-4841-96E4-61162382BEED}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
@@ -480,28 +460,25 @@
     <col min="4" max="4" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -563,46 +540,6 @@
       </c>
       <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1">
-        <v>50</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1">
-        <v>90</v>
-      </c>
-      <c r="E5" s="1">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1">
-        <v>45</v>
-      </c>
-      <c r="C6" s="1">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1">
-        <v>45</v>
-      </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
